--- a/모의고사/코코모의고사1회_정답.xlsx
+++ b/모의고사/코코모의고사1회_정답.xlsx
@@ -29,7 +29,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0&quot;개&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,11 +40,17 @@
     <font>
       <name val="돋움"/>
       <b val="1"/>
-      <color rgb="000000FF"/>
+      <color rgb="000070C0"/>
       <sz val="16"/>
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -135,7 +141,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -154,7 +160,7 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -163,7 +169,7 @@
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="000000FF"/>
+        <color rgb="000070C0"/>
       </font>
     </dxf>
   </dxfs>
